--- a/artfynd/A 5454-2022 artfynd.xlsx
+++ b/artfynd/A 5454-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5454-2022 artfynd.xlsx
+++ b/artfynd/A 5454-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111947297</v>
+        <v>17177449</v>
       </c>
       <c r="B2" t="n">
-        <v>85388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663735</v>
+        <v>663749</v>
       </c>
       <c r="R2" t="n">
-        <v>6710544</v>
+        <v>6710683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2015-03-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2015-03-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +768,1406 @@
           <t>Karin Wiklund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>103351115</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>663736</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6710667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103351118</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>53</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>663735</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6710675</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103351116</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>663735</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6710675</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>76283685</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S.V om Lerorna NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>663674</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6710519</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>76283684</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S.V om Lerorna NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>663671</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6710522</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111947297</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>663735</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710544</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>76283686</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S.V om Lerorna NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>663671</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710527</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111947296</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>663666</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6710458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16629262</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>663763</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6710896</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94647040</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lerorna, 90 m S om sydspetsen på sjön i naturreservatet, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>663659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6710531</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100400874</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>S om Lerornas NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>663660</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6710493</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 4 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre, högvuxen granskog med inslag av grova tallar</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103351126</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lerorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>663675</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6710505</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100401151</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SV om Lerornas NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>663669</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6710501</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre högvuxen granskog med inslag av grova tallar</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>

--- a/artfynd/A 5454-2022 artfynd.xlsx
+++ b/artfynd/A 5454-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17177449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103351115</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103351118</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103351116</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76283685</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76283684</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947297</t>
         </is>
       </c>
     </row>
@@ -1496,6 +1536,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76283686</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947296</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16629262</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94647040</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100400874</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103351126</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,8 +2242,29 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100401151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>